--- a/Log Sheet.xlsx
+++ b/Log Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Datasets\Offline AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2B2E8B-F3CA-41DB-BC37-045A1708568F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC2CF89-C01F-4FB7-A7A4-75E2E3C928F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Date</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>Status_Description</t>
+  </si>
+  <si>
+    <t>Model_Name</t>
   </si>
 </sst>
 </file>
@@ -390,19 +393,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="4" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -410,25 +414,29 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>